--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127636659</v>
+        <v>127636634</v>
       </c>
       <c r="B7" t="n">
-        <v>91330</v>
+        <v>57821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,24 +1221,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
@@ -1278,14 +1287,19 @@
           <t>2025-08-17</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med ulltickeporing</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127636634</v>
+        <v>127636659</v>
       </c>
       <c r="B8" t="n">
-        <v>57821</v>
+        <v>91330</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,33 +1337,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
@@ -1389,19 +1394,14 @@
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:35</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Med ulltickeporing</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1640,6 +1640,2462 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127727445</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>658</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>544738</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7243982</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127727424</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>544711</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7243945</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska barkfläng</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127727428</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>544818</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7244249</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127727435</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>544950</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7244174</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127727446</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91699</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>544738</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7243982</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127727477</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>544707</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7243954</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Finns spritt i hela området</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127727448</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58031</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>544763</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7244177</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127727456</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>544702</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7244024</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkropp</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127727432</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>544776</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7244208</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127727461</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>544745</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7243980</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Granhögstubbe, knäckt och låga</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe, knäckt och låga</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127727440</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>544719</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7243926</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127727420</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>544731</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7244010</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127727450</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>544610</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7244010</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>granstubbe och låga nyknäckt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # granstubbe och låga nyknäckt</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127727447</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57765</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>544765</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7244175</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127727452</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>544617</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7244014</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Stående levande</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående levande</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127727476</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>544893</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7244090</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127727455</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>544709</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7243986</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkropp</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127727439</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>544787</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7243985</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127727441</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>544694</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7244102</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127727434</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>544970</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7244170</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127727444</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skansnäsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>544738</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7243982</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127636629</v>
       </c>
       <c r="B2" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>127636726</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127639404</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127639421</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>127636864</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127636634</v>
       </c>
       <c r="B7" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>127636659</v>
       </c>
       <c r="B8" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>127639294</v>
       </c>
       <c r="B9" t="n">
-        <v>91699</v>
+        <v>91701</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>127636836</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>127727445</v>
       </c>
       <c r="B11" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127727424</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>127727428</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,50 +2008,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727435</v>
+        <v>127727446</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>91701</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544950</v>
+        <v>544738</v>
       </c>
       <c r="R14" t="n">
-        <v>7244174</v>
+        <v>7243982</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2086,11 +2081,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2110,9 +2100,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2130,45 +2125,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727446</v>
+        <v>127727435</v>
       </c>
       <c r="B15" t="n">
-        <v>91699</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544738</v>
+        <v>544950</v>
       </c>
       <c r="R15" t="n">
-        <v>7243982</v>
+        <v>7244174</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2203,6 +2203,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2222,14 +2227,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2250,7 +2250,7 @@
         <v>127727477</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>127727448</v>
       </c>
       <c r="B17" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>127727456</v>
       </c>
       <c r="B18" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>127727432</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>127727461</v>
       </c>
       <c r="B20" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>127727440</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>127727420</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,45 +3046,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727450</v>
+        <v>127727447</v>
       </c>
       <c r="B23" t="n">
-        <v>91326</v>
+        <v>57767</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544610</v>
+        <v>544765</v>
       </c>
       <c r="R23" t="n">
-        <v>7244010</v>
+        <v>7244175</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3127,26 +3136,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>granstubbe och låga nyknäckt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies # granstubbe och låga nyknäckt</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3163,54 +3152,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727447</v>
+        <v>127727450</v>
       </c>
       <c r="B24" t="n">
-        <v>57765</v>
+        <v>91328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544765</v>
+        <v>544610</v>
       </c>
       <c r="R24" t="n">
-        <v>7244175</v>
+        <v>7244010</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3253,6 +3233,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>granstubbe och låga nyknäckt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies # granstubbe och låga nyknäckt</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3269,10 +3269,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127727452</v>
+        <v>127727476</v>
       </c>
       <c r="B25" t="n">
-        <v>91326</v>
+        <v>91350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3280,21 +3280,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544617</v>
+        <v>544893</v>
       </c>
       <c r="R25" t="n">
-        <v>7244014</v>
+        <v>7244090</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Stående levande</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3386,10 +3386,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127727476</v>
+        <v>127727452</v>
       </c>
       <c r="B26" t="n">
-        <v>91348</v>
+        <v>91328</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3397,21 +3397,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544893</v>
+        <v>544617</v>
       </c>
       <c r="R26" t="n">
-        <v>7244090</v>
+        <v>7244014</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Stående levande</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3506,7 +3506,7 @@
         <v>127727455</v>
       </c>
       <c r="B27" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>127727439</v>
       </c>
       <c r="B28" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727441</v>
+        <v>127727434</v>
       </c>
       <c r="B29" t="n">
-        <v>57821</v>
+        <v>57663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3753,27 +3753,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544694</v>
+        <v>544970</v>
       </c>
       <c r="R29" t="n">
-        <v>7244102</v>
+        <v>7244170</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3818,6 +3818,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,10 +3864,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727434</v>
+        <v>127727441</v>
       </c>
       <c r="B30" t="n">
-        <v>57661</v>
+        <v>57823</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3870,27 +3875,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3899,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544970</v>
+        <v>544694</v>
       </c>
       <c r="R30" t="n">
-        <v>7244170</v>
+        <v>7244102</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3935,11 +3940,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3984,7 +3984,7 @@
         <v>127727444</v>
       </c>
       <c r="B31" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127636634</v>
+        <v>127636659</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>91332</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,33 +1221,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
@@ -1287,19 +1278,14 @@
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:35</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med ulltickeporing</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127636659</v>
+        <v>127636634</v>
       </c>
       <c r="B8" t="n">
-        <v>91332</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,24 +1323,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
@@ -1394,14 +1389,19 @@
           <t>2025-08-17</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Med ulltickeporing</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3046,54 +3046,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727447</v>
+        <v>127727450</v>
       </c>
       <c r="B23" t="n">
-        <v>57767</v>
+        <v>91328</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544765</v>
+        <v>544610</v>
       </c>
       <c r="R23" t="n">
-        <v>7244175</v>
+        <v>7244010</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3136,6 +3127,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>granstubbe och låga nyknäckt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # granstubbe och låga nyknäckt</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3152,45 +3163,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727450</v>
+        <v>127727447</v>
       </c>
       <c r="B24" t="n">
-        <v>91328</v>
+        <v>57767</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544610</v>
+        <v>544765</v>
       </c>
       <c r="R24" t="n">
-        <v>7244010</v>
+        <v>7244175</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3233,26 +3253,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>granstubbe och låga nyknäckt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies # granstubbe och låga nyknäckt</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3269,10 +3269,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127727476</v>
+        <v>127727452</v>
       </c>
       <c r="B25" t="n">
-        <v>91350</v>
+        <v>91328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3280,21 +3280,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544893</v>
+        <v>544617</v>
       </c>
       <c r="R25" t="n">
-        <v>7244090</v>
+        <v>7244014</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Stående levande</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3386,10 +3386,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127727452</v>
+        <v>127727476</v>
       </c>
       <c r="B26" t="n">
-        <v>91328</v>
+        <v>91350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3397,21 +3397,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544617</v>
+        <v>544893</v>
       </c>
       <c r="R26" t="n">
-        <v>7244014</v>
+        <v>7244090</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Stående levande</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727456</v>
+        <v>127727432</v>
       </c>
       <c r="B18" t="n">
-        <v>91328</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2462,34 +2462,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544702</v>
+        <v>544776</v>
       </c>
       <c r="R18" t="n">
-        <v>7244024</v>
+        <v>7244208</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2526,7 +2531,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Fjolårets fruktkropp</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2568,10 +2573,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727432</v>
+        <v>127727456</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>91328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,39 +2584,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544776</v>
+        <v>544702</v>
       </c>
       <c r="R19" t="n">
-        <v>7244208</v>
+        <v>7244024</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Fjolårets fruktkropp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3046,45 +3046,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727450</v>
+        <v>127727447</v>
       </c>
       <c r="B23" t="n">
-        <v>91328</v>
+        <v>57767</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544610</v>
+        <v>544765</v>
       </c>
       <c r="R23" t="n">
-        <v>7244010</v>
+        <v>7244175</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3127,26 +3136,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>granstubbe och låga nyknäckt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies # granstubbe och låga nyknäckt</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3163,54 +3152,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727447</v>
+        <v>127727450</v>
       </c>
       <c r="B24" t="n">
-        <v>57767</v>
+        <v>91328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544765</v>
+        <v>544610</v>
       </c>
       <c r="R24" t="n">
-        <v>7244175</v>
+        <v>7244010</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3253,6 +3233,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>granstubbe och låga nyknäckt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies # granstubbe och låga nyknäckt</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3269,10 +3269,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127727452</v>
+        <v>127727476</v>
       </c>
       <c r="B25" t="n">
-        <v>91328</v>
+        <v>91350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3280,21 +3280,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544617</v>
+        <v>544893</v>
       </c>
       <c r="R25" t="n">
-        <v>7244014</v>
+        <v>7244090</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Stående levande</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3386,10 +3386,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127727476</v>
+        <v>127727452</v>
       </c>
       <c r="B26" t="n">
-        <v>91350</v>
+        <v>91328</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3397,21 +3397,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544893</v>
+        <v>544617</v>
       </c>
       <c r="R26" t="n">
-        <v>7244090</v>
+        <v>7244014</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Stående levande</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127636629</v>
       </c>
       <c r="B2" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127636659</v>
       </c>
       <c r="B7" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>127639294</v>
       </c>
       <c r="B9" t="n">
-        <v>91701</v>
+        <v>91707</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>127727445</v>
       </c>
       <c r="B11" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2008,45 +2008,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727446</v>
+        <v>127727435</v>
       </c>
       <c r="B14" t="n">
-        <v>91701</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544738</v>
+        <v>544950</v>
       </c>
       <c r="R14" t="n">
-        <v>7243982</v>
+        <v>7244174</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,6 +2086,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2100,14 +2110,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2125,50 +2130,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727435</v>
+        <v>127727446</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>91707</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544950</v>
+        <v>544738</v>
       </c>
       <c r="R15" t="n">
-        <v>7244174</v>
+        <v>7243982</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2203,11 +2203,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2227,9 +2222,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727432</v>
+        <v>127727456</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>91334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2462,39 +2462,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544776</v>
+        <v>544702</v>
       </c>
       <c r="R18" t="n">
-        <v>7244208</v>
+        <v>7244024</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2531,7 +2526,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Fjolårets fruktkropp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727456</v>
+        <v>127727432</v>
       </c>
       <c r="B19" t="n">
-        <v>91328</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,34 +2579,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544702</v>
+        <v>544776</v>
       </c>
       <c r="R19" t="n">
-        <v>7244024</v>
+        <v>7244208</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Fjolårets fruktkropp</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2693,7 +2693,7 @@
         <v>127727461</v>
       </c>
       <c r="B20" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>127727420</v>
       </c>
       <c r="B22" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,54 +3046,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727447</v>
+        <v>127727450</v>
       </c>
       <c r="B23" t="n">
-        <v>57767</v>
+        <v>91334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544765</v>
+        <v>544610</v>
       </c>
       <c r="R23" t="n">
-        <v>7244175</v>
+        <v>7244010</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3136,6 +3127,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>granstubbe och låga nyknäckt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # granstubbe och låga nyknäckt</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3152,45 +3163,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727450</v>
+        <v>127727447</v>
       </c>
       <c r="B24" t="n">
-        <v>91328</v>
+        <v>57767</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544610</v>
+        <v>544765</v>
       </c>
       <c r="R24" t="n">
-        <v>7244010</v>
+        <v>7244175</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3233,26 +3253,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>granstubbe och låga nyknäckt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies # granstubbe och låga nyknäckt</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3272,7 +3272,7 @@
         <v>127727476</v>
       </c>
       <c r="B25" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>127727452</v>
       </c>
       <c r="B26" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>127727455</v>
       </c>
       <c r="B27" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727434</v>
+        <v>127727441</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3753,27 +3753,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544970</v>
+        <v>544694</v>
       </c>
       <c r="R29" t="n">
-        <v>7244170</v>
+        <v>7244102</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3818,11 +3818,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3864,10 +3859,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727441</v>
+        <v>127727434</v>
       </c>
       <c r="B30" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3875,27 +3870,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3904,10 +3899,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544694</v>
+        <v>544970</v>
       </c>
       <c r="R30" t="n">
-        <v>7244102</v>
+        <v>7244170</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3940,6 +3935,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3984,7 +3984,7 @@
         <v>127727444</v>
       </c>
       <c r="B31" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127636629</v>
+        <v>127636726</v>
       </c>
       <c r="B2" t="n">
-        <v>91696</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544770</v>
+        <v>544781</v>
       </c>
       <c r="R2" t="n">
-        <v>7244256</v>
+        <v>7244263</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Granlåga med ullticka och klibbticka</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,21 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127636726</v>
+        <v>127636629</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>91699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544781</v>
+        <v>544770</v>
       </c>
       <c r="R3" t="n">
-        <v>7244263</v>
+        <v>7244256</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Granlåga med ullticka och klibbticka</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,6 +868,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -902,7 +902,7 @@
         <v>127639404</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127639421</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>127636864</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127636659</v>
       </c>
       <c r="B7" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>127636634</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>127639294</v>
       </c>
       <c r="B9" t="n">
-        <v>91707</v>
+        <v>91710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>127636836</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>127727445</v>
       </c>
       <c r="B11" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127727424</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>127727428</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,50 +2008,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727435</v>
+        <v>127727446</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>91710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544950</v>
+        <v>544738</v>
       </c>
       <c r="R14" t="n">
-        <v>7244174</v>
+        <v>7243982</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2086,11 +2081,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2110,9 +2100,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2130,45 +2125,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727446</v>
+        <v>127727435</v>
       </c>
       <c r="B15" t="n">
-        <v>91707</v>
+        <v>57666</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544738</v>
+        <v>544950</v>
       </c>
       <c r="R15" t="n">
-        <v>7243982</v>
+        <v>7244174</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2203,6 +2203,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2222,14 +2227,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2250,7 +2250,7 @@
         <v>127727477</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>127727448</v>
       </c>
       <c r="B17" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>127727456</v>
       </c>
       <c r="B18" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>127727432</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>127727461</v>
       </c>
       <c r="B20" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>127727440</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>127727420</v>
       </c>
       <c r="B22" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,45 +3046,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727450</v>
+        <v>127727447</v>
       </c>
       <c r="B23" t="n">
-        <v>91334</v>
+        <v>57770</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544610</v>
+        <v>544765</v>
       </c>
       <c r="R23" t="n">
-        <v>7244010</v>
+        <v>7244175</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3127,26 +3136,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>granstubbe och låga nyknäckt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies # granstubbe och låga nyknäckt</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3163,54 +3152,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727447</v>
+        <v>127727450</v>
       </c>
       <c r="B24" t="n">
-        <v>57767</v>
+        <v>91337</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544765</v>
+        <v>544610</v>
       </c>
       <c r="R24" t="n">
-        <v>7244175</v>
+        <v>7244010</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3253,6 +3233,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>granstubbe och låga nyknäckt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies # granstubbe och låga nyknäckt</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3269,10 +3269,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127727476</v>
+        <v>127727452</v>
       </c>
       <c r="B25" t="n">
-        <v>91356</v>
+        <v>91337</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3280,21 +3280,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544893</v>
+        <v>544617</v>
       </c>
       <c r="R25" t="n">
-        <v>7244090</v>
+        <v>7244014</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Stående levande</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3386,10 +3386,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127727452</v>
+        <v>127727476</v>
       </c>
       <c r="B26" t="n">
-        <v>91334</v>
+        <v>91359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3397,21 +3397,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544617</v>
+        <v>544893</v>
       </c>
       <c r="R26" t="n">
-        <v>7244014</v>
+        <v>7244090</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Stående levande</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3506,7 +3506,7 @@
         <v>127727455</v>
       </c>
       <c r="B27" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>127727439</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727441</v>
+        <v>127727434</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>57666</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3753,27 +3753,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544694</v>
+        <v>544970</v>
       </c>
       <c r="R29" t="n">
-        <v>7244102</v>
+        <v>7244170</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3818,6 +3818,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,10 +3864,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727434</v>
+        <v>127727441</v>
       </c>
       <c r="B30" t="n">
-        <v>57663</v>
+        <v>57826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3870,27 +3875,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3899,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544970</v>
+        <v>544694</v>
       </c>
       <c r="R30" t="n">
-        <v>7244170</v>
+        <v>7244102</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3935,11 +3940,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3984,7 +3984,7 @@
         <v>127727444</v>
       </c>
       <c r="B31" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127636726</v>
+        <v>127636629</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>91707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544781</v>
+        <v>544770</v>
       </c>
       <c r="R2" t="n">
-        <v>7244263</v>
+        <v>7244256</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Granlåga med ullticka och klibbticka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,45 +792,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127636629</v>
+        <v>127636726</v>
       </c>
       <c r="B3" t="n">
-        <v>91699</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544770</v>
+        <v>544781</v>
       </c>
       <c r="R3" t="n">
-        <v>7244256</v>
+        <v>7244263</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Granlåga med ullticka och klibbticka</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,21 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -902,7 +902,7 @@
         <v>127639404</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127639421</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>127636864</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127636659</v>
       </c>
       <c r="B7" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>127636634</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>127639294</v>
       </c>
       <c r="B9" t="n">
-        <v>91710</v>
+        <v>91718</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>127636836</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>127727445</v>
       </c>
       <c r="B11" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127727424</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>127727428</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>127727446</v>
       </c>
       <c r="B14" t="n">
-        <v>91710</v>
+        <v>91718</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>127727435</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127727477</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>127727448</v>
       </c>
       <c r="B17" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>127727456</v>
       </c>
       <c r="B18" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>127727432</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>127727461</v>
       </c>
       <c r="B20" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>127727440</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>127727420</v>
       </c>
       <c r="B22" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,54 +3046,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727447</v>
+        <v>127727450</v>
       </c>
       <c r="B23" t="n">
-        <v>57770</v>
+        <v>91345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544765</v>
+        <v>544610</v>
       </c>
       <c r="R23" t="n">
-        <v>7244175</v>
+        <v>7244010</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3136,6 +3127,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>granstubbe och låga nyknäckt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # granstubbe och låga nyknäckt</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3152,45 +3163,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727450</v>
+        <v>127727447</v>
       </c>
       <c r="B24" t="n">
-        <v>91337</v>
+        <v>57776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544610</v>
+        <v>544765</v>
       </c>
       <c r="R24" t="n">
-        <v>7244010</v>
+        <v>7244175</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3233,26 +3253,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>granstubbe och låga nyknäckt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies # granstubbe och låga nyknäckt</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3272,7 +3272,7 @@
         <v>127727452</v>
       </c>
       <c r="B25" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>127727476</v>
       </c>
       <c r="B26" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>127727455</v>
       </c>
       <c r="B27" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>127727439</v>
       </c>
       <c r="B28" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>127727434</v>
       </c>
       <c r="B29" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127727441</v>
       </c>
       <c r="B30" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>127727444</v>
       </c>
       <c r="B31" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127636629</v>
+        <v>127636726</v>
       </c>
       <c r="B2" t="n">
-        <v>91707</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544770</v>
+        <v>544781</v>
       </c>
       <c r="R2" t="n">
-        <v>7244256</v>
+        <v>7244263</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Granlåga med ullticka och klibbticka</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,21 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127636726</v>
+        <v>127636629</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>91708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544781</v>
+        <v>544770</v>
       </c>
       <c r="R3" t="n">
-        <v>7244263</v>
+        <v>7244256</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Granlåga med ullticka och klibbticka</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,6 +868,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>127636659</v>
       </c>
       <c r="B7" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>127639294</v>
       </c>
       <c r="B9" t="n">
-        <v>91718</v>
+        <v>91719</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727445</v>
+        <v>127727424</v>
       </c>
       <c r="B11" t="n">
-        <v>91645</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,34 +1653,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544738</v>
+        <v>544711</v>
       </c>
       <c r="R11" t="n">
-        <v>7243982</v>
+        <v>7243945</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1715,6 +1720,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska barkfläng</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1734,14 +1744,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1759,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727424</v>
+        <v>127727445</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,39 +1775,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544711</v>
+        <v>544738</v>
       </c>
       <c r="R12" t="n">
-        <v>7243945</v>
+        <v>7243982</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1837,11 +1837,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska barkfläng</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1861,9 +1856,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
         <v>127727446</v>
       </c>
       <c r="B14" t="n">
-        <v>91718</v>
+        <v>91719</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>127727456</v>
       </c>
       <c r="B18" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>127727461</v>
       </c>
       <c r="B20" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>127727420</v>
       </c>
       <c r="B22" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>127727450</v>
       </c>
       <c r="B23" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>127727452</v>
       </c>
       <c r="B25" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>127727476</v>
       </c>
       <c r="B26" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>127727455</v>
       </c>
       <c r="B27" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727434</v>
+        <v>127727441</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3753,27 +3753,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544970</v>
+        <v>544694</v>
       </c>
       <c r="R29" t="n">
-        <v>7244170</v>
+        <v>7244102</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3818,11 +3818,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3864,10 +3859,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727441</v>
+        <v>127727434</v>
       </c>
       <c r="B30" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3875,27 +3870,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3904,10 +3899,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544694</v>
+        <v>544970</v>
       </c>
       <c r="R30" t="n">
-        <v>7244102</v>
+        <v>7244170</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3940,6 +3935,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3984,7 +3984,7 @@
         <v>127727444</v>
       </c>
       <c r="B31" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127636726</v>
+        <v>127636629</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>91709</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544781</v>
+        <v>544770</v>
       </c>
       <c r="R2" t="n">
-        <v>7244263</v>
+        <v>7244256</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Granlåga med ullticka och klibbticka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,45 +792,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127636629</v>
+        <v>127636726</v>
       </c>
       <c r="B3" t="n">
-        <v>91708</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544770</v>
+        <v>544781</v>
       </c>
       <c r="R3" t="n">
-        <v>7244256</v>
+        <v>7244263</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Granlåga med ullticka och klibbticka</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,21 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>127636659</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>127639294</v>
       </c>
       <c r="B9" t="n">
-        <v>91719</v>
+        <v>91720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727424</v>
+        <v>127727445</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>91647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,39 +1653,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544711</v>
+        <v>544738</v>
       </c>
       <c r="R11" t="n">
-        <v>7243945</v>
+        <v>7243982</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1720,11 +1715,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska barkfläng</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1744,9 +1734,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1764,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727445</v>
+        <v>127727424</v>
       </c>
       <c r="B12" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,34 +1770,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544738</v>
+        <v>544711</v>
       </c>
       <c r="R12" t="n">
-        <v>7243982</v>
+        <v>7243945</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1837,6 +1837,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska barkfläng</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1856,14 +1861,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
         <v>127727446</v>
       </c>
       <c r="B14" t="n">
-        <v>91719</v>
+        <v>91720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>127727456</v>
       </c>
       <c r="B18" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>127727461</v>
       </c>
       <c r="B20" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>127727420</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>127727450</v>
       </c>
       <c r="B23" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>127727452</v>
       </c>
       <c r="B25" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>127727476</v>
       </c>
       <c r="B26" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>127727455</v>
       </c>
       <c r="B27" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727441</v>
+        <v>127727434</v>
       </c>
       <c r="B29" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3753,27 +3753,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544694</v>
+        <v>544970</v>
       </c>
       <c r="R29" t="n">
-        <v>7244102</v>
+        <v>7244170</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3818,6 +3818,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,10 +3864,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727434</v>
+        <v>127727441</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3870,27 +3875,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3899,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544970</v>
+        <v>544694</v>
       </c>
       <c r="R30" t="n">
-        <v>7244170</v>
+        <v>7244102</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3935,11 +3940,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3984,7 +3984,7 @@
         <v>127727444</v>
       </c>
       <c r="B31" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127636629</v>
       </c>
       <c r="B2" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127636659</v>
       </c>
       <c r="B7" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>127639294</v>
       </c>
       <c r="B9" t="n">
-        <v>91720</v>
+        <v>91721</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727445</v>
+        <v>127727424</v>
       </c>
       <c r="B11" t="n">
-        <v>91647</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,34 +1653,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544738</v>
+        <v>544711</v>
       </c>
       <c r="R11" t="n">
-        <v>7243982</v>
+        <v>7243945</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1715,6 +1720,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska barkfläng</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1734,14 +1744,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1759,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727424</v>
+        <v>127727445</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>91648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,39 +1775,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544711</v>
+        <v>544738</v>
       </c>
       <c r="R12" t="n">
-        <v>7243945</v>
+        <v>7243982</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1837,11 +1837,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska barkfläng</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1861,9 +1856,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
         <v>127727446</v>
       </c>
       <c r="B14" t="n">
-        <v>91720</v>
+        <v>91721</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727456</v>
+        <v>127727432</v>
       </c>
       <c r="B18" t="n">
-        <v>91347</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2462,34 +2462,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544702</v>
+        <v>544776</v>
       </c>
       <c r="R18" t="n">
-        <v>7244024</v>
+        <v>7244208</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2526,7 +2531,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Fjolårets fruktkropp</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2568,10 +2573,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727432</v>
+        <v>127727456</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,39 +2584,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544776</v>
+        <v>544702</v>
       </c>
       <c r="R19" t="n">
-        <v>7244208</v>
+        <v>7244024</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Fjolårets fruktkropp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2693,7 +2693,7 @@
         <v>127727461</v>
       </c>
       <c r="B20" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>127727420</v>
       </c>
       <c r="B22" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>127727450</v>
       </c>
       <c r="B23" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>127727452</v>
       </c>
       <c r="B25" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>127727476</v>
       </c>
       <c r="B26" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>127727455</v>
       </c>
       <c r="B27" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>127727444</v>
       </c>
       <c r="B31" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127636659</v>
+        <v>127636634</v>
       </c>
       <c r="B7" t="n">
-        <v>91352</v>
+        <v>57832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,24 +1221,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
@@ -1278,14 +1287,19 @@
           <t>2025-08-17</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med ulltickeporing</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127636634</v>
+        <v>127636659</v>
       </c>
       <c r="B8" t="n">
-        <v>57832</v>
+        <v>91352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,33 +1337,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
@@ -1389,19 +1394,14 @@
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:35</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Med ulltickeporing</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1642,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727424</v>
+        <v>127727445</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>91648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,39 +1653,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544711</v>
+        <v>544738</v>
       </c>
       <c r="R11" t="n">
-        <v>7243945</v>
+        <v>7243982</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1720,11 +1715,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska barkfläng</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1744,9 +1734,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1764,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727445</v>
+        <v>127727424</v>
       </c>
       <c r="B12" t="n">
-        <v>91648</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,34 +1770,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544738</v>
+        <v>544711</v>
       </c>
       <c r="R12" t="n">
-        <v>7243982</v>
+        <v>7243945</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1837,6 +1837,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska barkfläng</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1856,14 +1861,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127636634</v>
+        <v>127636659</v>
       </c>
       <c r="B7" t="n">
-        <v>57832</v>
+        <v>91352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,33 +1221,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
@@ -1287,19 +1278,14 @@
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:35</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med ulltickeporing</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127636659</v>
+        <v>127636634</v>
       </c>
       <c r="B8" t="n">
-        <v>91352</v>
+        <v>57832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,24 +1323,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
@@ -1394,14 +1389,19 @@
           <t>2025-08-17</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Med ulltickeporing</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127636659</v>
+        <v>127636634</v>
       </c>
       <c r="B7" t="n">
-        <v>91352</v>
+        <v>57832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,24 +1221,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
@@ -1278,14 +1287,19 @@
           <t>2025-08-17</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med ulltickeporing</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127636634</v>
+        <v>127636659</v>
       </c>
       <c r="B8" t="n">
-        <v>57832</v>
+        <v>91352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,33 +1337,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
@@ -1389,19 +1394,14 @@
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:35</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Med ulltickeporing</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727432</v>
+        <v>127727456</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2462,39 +2462,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544776</v>
+        <v>544702</v>
       </c>
       <c r="R18" t="n">
-        <v>7244208</v>
+        <v>7244024</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2531,7 +2526,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Fjolårets fruktkropp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727456</v>
+        <v>127727432</v>
       </c>
       <c r="B19" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,34 +2579,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544702</v>
+        <v>544776</v>
       </c>
       <c r="R19" t="n">
-        <v>7244024</v>
+        <v>7244208</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Fjolårets fruktkropp</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3046,45 +3046,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727450</v>
+        <v>127727447</v>
       </c>
       <c r="B23" t="n">
-        <v>91348</v>
+        <v>57776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544610</v>
+        <v>544765</v>
       </c>
       <c r="R23" t="n">
-        <v>7244010</v>
+        <v>7244175</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3127,26 +3136,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>granstubbe och låga nyknäckt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies # granstubbe och låga nyknäckt</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3163,54 +3152,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727447</v>
+        <v>127727450</v>
       </c>
       <c r="B24" t="n">
-        <v>57776</v>
+        <v>91348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544765</v>
+        <v>544610</v>
       </c>
       <c r="R24" t="n">
-        <v>7244175</v>
+        <v>7244010</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3253,6 +3233,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>granstubbe och låga nyknäckt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies # granstubbe och låga nyknäckt</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -1645,7 +1645,7 @@
         <v>127727445</v>
       </c>
       <c r="B11" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127727424</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>127727428</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,45 +2008,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727446</v>
+        <v>127727435</v>
       </c>
       <c r="B14" t="n">
-        <v>91721</v>
+        <v>57673</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544738</v>
+        <v>544950</v>
       </c>
       <c r="R14" t="n">
-        <v>7243982</v>
+        <v>7244174</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,6 +2086,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2100,14 +2110,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2125,50 +2130,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727435</v>
+        <v>127727446</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>91729</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544950</v>
+        <v>544738</v>
       </c>
       <c r="R15" t="n">
-        <v>7244174</v>
+        <v>7243982</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2203,11 +2203,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2227,9 +2222,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2250,7 +2250,7 @@
         <v>127727477</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>127727448</v>
       </c>
       <c r="B17" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>127727456</v>
       </c>
       <c r="B18" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>127727432</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>127727461</v>
       </c>
       <c r="B20" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>127727440</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>127727420</v>
       </c>
       <c r="B22" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>127727447</v>
       </c>
       <c r="B23" t="n">
-        <v>57776</v>
+        <v>57777</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>127727450</v>
       </c>
       <c r="B24" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>127727452</v>
       </c>
       <c r="B25" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>127727476</v>
       </c>
       <c r="B26" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>127727455</v>
       </c>
       <c r="B27" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>127727439</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>127727434</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127727441</v>
       </c>
       <c r="B30" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>127727444</v>
       </c>
       <c r="B31" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -2008,50 +2008,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727435</v>
+        <v>127727446</v>
       </c>
       <c r="B14" t="n">
-        <v>57673</v>
+        <v>91729</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544950</v>
+        <v>544738</v>
       </c>
       <c r="R14" t="n">
-        <v>7244174</v>
+        <v>7243982</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2086,11 +2081,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2110,9 +2100,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2130,45 +2125,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727446</v>
+        <v>127727435</v>
       </c>
       <c r="B15" t="n">
-        <v>91729</v>
+        <v>57673</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544738</v>
+        <v>544950</v>
       </c>
       <c r="R15" t="n">
-        <v>7243982</v>
+        <v>7244174</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2203,6 +2203,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2222,14 +2227,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -3046,54 +3046,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727447</v>
+        <v>127727450</v>
       </c>
       <c r="B23" t="n">
-        <v>57777</v>
+        <v>91356</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544765</v>
+        <v>544610</v>
       </c>
       <c r="R23" t="n">
-        <v>7244175</v>
+        <v>7244010</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3136,6 +3127,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>granstubbe och låga nyknäckt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # granstubbe och låga nyknäckt</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3152,45 +3163,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727450</v>
+        <v>127727447</v>
       </c>
       <c r="B24" t="n">
-        <v>91356</v>
+        <v>57777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544610</v>
+        <v>544765</v>
       </c>
       <c r="R24" t="n">
-        <v>7244010</v>
+        <v>7244175</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3233,26 +3253,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>granstubbe och låga nyknäckt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies # granstubbe och låga nyknäckt</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -1642,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727445</v>
+        <v>127727424</v>
       </c>
       <c r="B11" t="n">
-        <v>91656</v>
+        <v>57684</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,34 +1653,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544738</v>
+        <v>544711</v>
       </c>
       <c r="R11" t="n">
-        <v>7243982</v>
+        <v>7243945</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1715,6 +1720,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska barkfläng</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1734,14 +1744,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1759,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727424</v>
+        <v>127727445</v>
       </c>
       <c r="B12" t="n">
-        <v>57673</v>
+        <v>91667</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,39 +1775,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544711</v>
+        <v>544738</v>
       </c>
       <c r="R12" t="n">
-        <v>7243945</v>
+        <v>7243982</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1837,11 +1837,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska barkfläng</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1861,9 +1856,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1884,7 +1884,7 @@
         <v>127727428</v>
       </c>
       <c r="B13" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>127727446</v>
       </c>
       <c r="B14" t="n">
-        <v>91729</v>
+        <v>91740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>127727435</v>
       </c>
       <c r="B15" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127727477</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>127727448</v>
       </c>
       <c r="B17" t="n">
-        <v>58043</v>
+        <v>58054</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>127727456</v>
       </c>
       <c r="B18" t="n">
-        <v>91356</v>
+        <v>91367</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>127727432</v>
       </c>
       <c r="B19" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>127727461</v>
       </c>
       <c r="B20" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>127727440</v>
       </c>
       <c r="B21" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>127727420</v>
       </c>
       <c r="B22" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>127727450</v>
       </c>
       <c r="B23" t="n">
-        <v>91356</v>
+        <v>91367</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>127727447</v>
       </c>
       <c r="B24" t="n">
-        <v>57777</v>
+        <v>57788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>127727452</v>
       </c>
       <c r="B25" t="n">
-        <v>91356</v>
+        <v>91367</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>127727476</v>
       </c>
       <c r="B26" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>127727455</v>
       </c>
       <c r="B27" t="n">
-        <v>91356</v>
+        <v>91367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>127727439</v>
       </c>
       <c r="B28" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>127727434</v>
       </c>
       <c r="B29" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127727441</v>
       </c>
       <c r="B30" t="n">
-        <v>57833</v>
+        <v>57844</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>127727444</v>
       </c>
       <c r="B31" t="n">
-        <v>91356</v>
+        <v>91367</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>

--- a/artfynd/A 14963-2022 artfynd.xlsx
+++ b/artfynd/A 14963-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127636629</v>
+        <v>127727445</v>
       </c>
       <c r="B2" t="n">
-        <v>91710</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544770</v>
+        <v>544738</v>
       </c>
       <c r="R2" t="n">
-        <v>7244256</v>
+        <v>7243982</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Granlåga med ullticka och klibbticka</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,38 +759,43 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>ullticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127636726</v>
+        <v>127727444</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544781</v>
+        <v>544738</v>
       </c>
       <c r="R3" t="n">
-        <v>7244263</v>
+        <v>7243982</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,17 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,26 +873,46 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127639404</v>
+        <v>127727450</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544656</v>
+        <v>544610</v>
       </c>
       <c r="R4" t="n">
-        <v>7244034</v>
+        <v>7244010</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,12 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,26 +990,46 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>granstubbe och låga nyknäckt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # granstubbe och låga nyknäckt</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127639421</v>
+        <v>127727452</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,36 +1037,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544630</v>
+        <v>544617</v>
       </c>
       <c r="R5" t="n">
         <v>7244014</v>
@@ -1071,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,26 +1107,46 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Stående levande</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående levande</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127636864</v>
+        <v>127727455</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544788</v>
+        <v>544709</v>
       </c>
       <c r="R6" t="n">
-        <v>7244261</v>
+        <v>7243986</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,17 +1208,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Inte äldre än 5 år</t>
+          <t>Fjolårets fruktkropp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,26 +1229,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127636659</v>
+        <v>127727456</v>
       </c>
       <c r="B7" t="n">
-        <v>91352</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544770</v>
+        <v>544702</v>
       </c>
       <c r="R7" t="n">
-        <v>7244256</v>
+        <v>7244024</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1275,17 +1325,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Med ulltickeporing</t>
+          <t>Fjolårets fruktkropp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,26 +1346,41 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127636634</v>
+        <v>127636659</v>
       </c>
       <c r="B8" t="n">
-        <v>57832</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,33 +1388,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
@@ -1389,19 +1445,14 @@
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:35</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Med ulltickeporing</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,32 +1479,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127639294</v>
+        <v>127727420</v>
       </c>
       <c r="B9" t="n">
-        <v>91721</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544671</v>
+        <v>544731</v>
       </c>
       <c r="R9" t="n">
-        <v>7244043</v>
+        <v>7244010</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1493,17 +1544,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Granlåga rotknäckt</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,52 +1571,57 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127636836</v>
+        <v>127639294</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>92292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544781</v>
+        <v>544671</v>
       </c>
       <c r="R10" t="n">
-        <v>7244263</v>
+        <v>7244043</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1618,6 +1669,11 @@
           <t>2025-08-17</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Granlåga rotknäckt</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1626,6 +1682,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1642,50 +1713,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727424</v>
+        <v>127727446</v>
       </c>
       <c r="B11" t="n">
-        <v>57684</v>
+        <v>92292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544711</v>
+        <v>544738</v>
       </c>
       <c r="R11" t="n">
-        <v>7243945</v>
+        <v>7243982</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1720,16 +1786,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska barkfläng</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1744,9 +1805,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1764,32 +1830,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727445</v>
+        <v>127636629</v>
       </c>
       <c r="B12" t="n">
-        <v>91667</v>
+        <v>92281</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544738</v>
+        <v>544770</v>
       </c>
       <c r="R12" t="n">
-        <v>7243982</v>
+        <v>7244256</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1829,12 +1895,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Granlåga med ullticka och klibbticka</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,83 +1919,73 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>ullticka</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127727428</v>
+        <v>127636836</v>
       </c>
       <c r="B13" t="n">
-        <v>57684</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544818</v>
+        <v>544781</v>
       </c>
       <c r="R13" t="n">
-        <v>7244249</v>
+        <v>7244263</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1951,17 +2012,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,46 +2028,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727446</v>
+        <v>127727477</v>
       </c>
       <c r="B14" t="n">
-        <v>91740</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2019,21 +2055,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,13 +2079,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544738</v>
+        <v>544707</v>
       </c>
       <c r="R14" t="n">
-        <v>7243982</v>
+        <v>7243954</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2081,6 +2117,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Finns spritt i hela området</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2089,26 +2130,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2125,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727435</v>
+        <v>127636726</v>
       </c>
       <c r="B15" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544950</v>
+        <v>544781</v>
       </c>
       <c r="R15" t="n">
-        <v>7244174</v>
+        <v>7244263</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2195,17 +2216,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2216,41 +2237,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127727477</v>
+        <v>127636864</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,37 +2264,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544707</v>
+        <v>544788</v>
       </c>
       <c r="R16" t="n">
-        <v>7243954</v>
+        <v>7244261</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2312,17 +2323,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Finns spritt i hela området</t>
+          <t>Inte äldre än 5 år</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,39 +2348,39 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727448</v>
+        <v>127639404</v>
       </c>
       <c r="B17" t="n">
-        <v>58054</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2380,7 +2391,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2389,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544763</v>
+        <v>544656</v>
       </c>
       <c r="R17" t="n">
-        <v>7244177</v>
+        <v>7244034</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2419,12 +2430,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2439,22 +2450,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727456</v>
+        <v>127639421</v>
       </c>
       <c r="B18" t="n">
-        <v>91367</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2462,34 +2473,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544702</v>
+        <v>544630</v>
       </c>
       <c r="R18" t="n">
-        <v>7244024</v>
+        <v>7244014</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2516,17 +2532,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkropp</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2537,41 +2548,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727432</v>
+        <v>127727424</v>
       </c>
       <c r="B19" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2595,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2608,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544776</v>
+        <v>544711</v>
       </c>
       <c r="R19" t="n">
-        <v>7244208</v>
+        <v>7243945</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2648,14 +2644,14 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska barkfläng</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
@@ -2690,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127727461</v>
+        <v>127727428</v>
       </c>
       <c r="B20" t="n">
-        <v>91389</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,34 +2697,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544745</v>
+        <v>544818</v>
       </c>
       <c r="R20" t="n">
-        <v>7243980</v>
+        <v>7244249</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2763,6 +2764,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2784,12 +2790,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt och låga</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt och låga</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2807,10 +2813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727440</v>
+        <v>127727432</v>
       </c>
       <c r="B21" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2844,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2847,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544719</v>
+        <v>544776</v>
       </c>
       <c r="R21" t="n">
-        <v>7243926</v>
+        <v>7244208</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2929,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727420</v>
+        <v>127727434</v>
       </c>
       <c r="B22" t="n">
-        <v>91371</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2940,34 +2946,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544731</v>
+        <v>544970</v>
       </c>
       <c r="R22" t="n">
-        <v>7244010</v>
+        <v>7244170</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3002,6 +3013,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3021,14 +3037,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3046,10 +3057,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727450</v>
+        <v>127727435</v>
       </c>
       <c r="B23" t="n">
-        <v>91367</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,34 +3068,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544610</v>
+        <v>544950</v>
       </c>
       <c r="R23" t="n">
-        <v>7244010</v>
+        <v>7244174</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3119,6 +3135,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3138,14 +3159,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>granstubbe och låga nyknäckt</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # granstubbe och låga nyknäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3163,27 +3179,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727447</v>
+        <v>127727438</v>
       </c>
       <c r="B24" t="n">
-        <v>57788</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3191,14 +3207,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3207,10 +3219,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544765</v>
+        <v>544922</v>
       </c>
       <c r="R24" t="n">
-        <v>7244175</v>
+        <v>7244247</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3245,6 +3257,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3253,6 +3270,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3269,10 +3301,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127727452</v>
+        <v>127727439</v>
       </c>
       <c r="B25" t="n">
-        <v>91367</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3280,34 +3312,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544617</v>
+        <v>544787</v>
       </c>
       <c r="R25" t="n">
-        <v>7244014</v>
+        <v>7243985</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3342,6 +3379,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3361,14 +3403,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Stående levande</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Stående levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3386,10 +3423,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127727476</v>
+        <v>127727440</v>
       </c>
       <c r="B26" t="n">
-        <v>91389</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3397,34 +3434,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544893</v>
+        <v>544719</v>
       </c>
       <c r="R26" t="n">
-        <v>7244090</v>
+        <v>7243926</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3459,6 +3501,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3478,14 +3525,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3503,45 +3545,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127727455</v>
+        <v>127727448</v>
       </c>
       <c r="B27" t="n">
-        <v>91367</v>
+        <v>58327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544709</v>
+        <v>544763</v>
       </c>
       <c r="R27" t="n">
-        <v>7243986</v>
+        <v>7244177</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3576,11 +3623,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkropp</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3589,21 +3631,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3620,27 +3647,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127727439</v>
+        <v>127727449</v>
       </c>
       <c r="B28" t="n">
-        <v>57684</v>
+        <v>58327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3651,7 +3678,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3660,10 +3687,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544787</v>
+        <v>544923</v>
       </c>
       <c r="R28" t="n">
-        <v>7243985</v>
+        <v>7244246</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3698,11 +3725,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3711,21 +3733,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3742,10 +3749,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727434</v>
+        <v>127636634</v>
       </c>
       <c r="B29" t="n">
-        <v>57684</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3753,27 +3760,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3782,10 +3793,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544970</v>
+        <v>544770</v>
       </c>
       <c r="R29" t="n">
-        <v>7244170</v>
+        <v>7244256</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3812,17 +3823,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3833,31 +3849,16 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3867,7 +3868,7 @@
         <v>127727441</v>
       </c>
       <c r="B30" t="n">
-        <v>57844</v>
+        <v>58114</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3981,10 +3982,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127727444</v>
+        <v>127727447</v>
       </c>
       <c r="B31" t="n">
-        <v>91367</v>
+        <v>58057</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3992,34 +3993,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544738</v>
+        <v>544765</v>
       </c>
       <c r="R31" t="n">
-        <v>7243982</v>
+        <v>7244175</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4062,26 +4072,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
